--- a/data/LGP-Menu.xlsx
+++ b/data/LGP-Menu.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\QR1PEPF00005878\EXCELCNV\0c466152-c767-4433-9da1-dce5be5e872a\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C874026-7E46-4FEC-B054-CD837B99AD2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0B67B2B-8994-4935-AE9F-A2660FDDBE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="200">
   <si>
     <t>id</t>
   </si>
@@ -561,6 +561,84 @@
   </si>
   <si>
     <t>6 Onz</t>
+  </si>
+  <si>
+    <t>PROP-500</t>
+  </si>
+  <si>
+    <t>Propina o Cobro Adicional</t>
+  </si>
+  <si>
+    <t>Propina o Cobro Adicional $5.00</t>
+  </si>
+  <si>
+    <t>$5.00 MXN</t>
+  </si>
+  <si>
+    <t>Gracias por su propina o cobro Adicional $5.00 MXN</t>
+  </si>
+  <si>
+    <t>Propina-5</t>
+  </si>
+  <si>
+    <t>PROP-501</t>
+  </si>
+  <si>
+    <t>Propina o Cobro Adicional $10.00</t>
+  </si>
+  <si>
+    <t>$10.00 MXN</t>
+  </si>
+  <si>
+    <t>Gracias por su propina o cobro Adicional $10.00 MXN</t>
+  </si>
+  <si>
+    <t>Propina-10</t>
+  </si>
+  <si>
+    <t>PROP-502</t>
+  </si>
+  <si>
+    <t>Propina o Cobro Adicional $20.00</t>
+  </si>
+  <si>
+    <t>$20.00 MXN</t>
+  </si>
+  <si>
+    <t>Gracias por su propina o cobro Adicional $20.00 MXN</t>
+  </si>
+  <si>
+    <t>Propina-20</t>
+  </si>
+  <si>
+    <t>PROP-503</t>
+  </si>
+  <si>
+    <t>Propina o Cobro Adicional $50.00</t>
+  </si>
+  <si>
+    <t>$50.00 MXN</t>
+  </si>
+  <si>
+    <t>Gracias por su propina o cobro Adicional $50.00 MXN</t>
+  </si>
+  <si>
+    <t>Propina-50</t>
+  </si>
+  <si>
+    <t>PROP-504</t>
+  </si>
+  <si>
+    <t>Propina o Cobro Adicional $100.00</t>
+  </si>
+  <si>
+    <t>$100.00 MXN</t>
+  </si>
+  <si>
+    <t>Gracias por su propina o cobro Adicional $100.00 MXN</t>
+  </si>
+  <si>
+    <t>Propina-100</t>
   </si>
 </sst>
 </file>
@@ -941,14 +1019,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="25.140625" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.5703125" customWidth="1"/>
     <col min="7" max="7" width="61.7109375" customWidth="1"/>
     <col min="8" max="8" width="22.28515625" customWidth="1"/>
@@ -2532,7 +2610,7 @@
         <v>168</v>
       </c>
       <c r="B36" s="2">
-        <v>307</v>
+        <v>401</v>
       </c>
       <c r="C36" t="s">
         <v>165</v>
@@ -2576,7 +2654,7 @@
         <v>171</v>
       </c>
       <c r="B37" s="2">
-        <v>307</v>
+        <v>402</v>
       </c>
       <c r="C37" t="s">
         <v>165</v>
@@ -2612,6 +2690,226 @@
         <v>165</v>
       </c>
       <c r="N37" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>174</v>
+      </c>
+      <c r="B38" s="2">
+        <v>500</v>
+      </c>
+      <c r="C38" t="s">
+        <v>175</v>
+      </c>
+      <c r="D38" t="s">
+        <v>175</v>
+      </c>
+      <c r="E38" t="s">
+        <v>176</v>
+      </c>
+      <c r="F38" t="s">
+        <v>177</v>
+      </c>
+      <c r="G38" t="s">
+        <v>178</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="4">
+        <v>5</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M38" t="s">
+        <v>179</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>180</v>
+      </c>
+      <c r="B39" s="2">
+        <v>501</v>
+      </c>
+      <c r="C39" t="s">
+        <v>175</v>
+      </c>
+      <c r="D39" t="s">
+        <v>175</v>
+      </c>
+      <c r="E39" t="s">
+        <v>181</v>
+      </c>
+      <c r="F39" t="s">
+        <v>182</v>
+      </c>
+      <c r="G39" t="s">
+        <v>183</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I39" s="4">
+        <v>10</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M39" t="s">
+        <v>184</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
+        <v>185</v>
+      </c>
+      <c r="B40" s="2">
+        <v>502</v>
+      </c>
+      <c r="C40" t="s">
+        <v>175</v>
+      </c>
+      <c r="D40" t="s">
+        <v>175</v>
+      </c>
+      <c r="E40" t="s">
+        <v>186</v>
+      </c>
+      <c r="F40" t="s">
+        <v>187</v>
+      </c>
+      <c r="G40" t="s">
+        <v>188</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40" s="4">
+        <v>20</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M40" t="s">
+        <v>189</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" t="s">
+        <v>190</v>
+      </c>
+      <c r="B41" s="2">
+        <v>503</v>
+      </c>
+      <c r="C41" t="s">
+        <v>175</v>
+      </c>
+      <c r="D41" t="s">
+        <v>175</v>
+      </c>
+      <c r="E41" t="s">
+        <v>191</v>
+      </c>
+      <c r="F41" t="s">
+        <v>192</v>
+      </c>
+      <c r="G41" t="s">
+        <v>193</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I41" s="4">
+        <v>50</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M41" t="s">
+        <v>194</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" t="s">
+        <v>195</v>
+      </c>
+      <c r="B42" s="2">
+        <v>504</v>
+      </c>
+      <c r="C42" t="s">
+        <v>175</v>
+      </c>
+      <c r="D42" t="s">
+        <v>175</v>
+      </c>
+      <c r="E42" t="s">
+        <v>196</v>
+      </c>
+      <c r="F42" t="s">
+        <v>197</v>
+      </c>
+      <c r="G42" t="s">
+        <v>198</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" s="4">
+        <v>100</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M42" t="s">
+        <v>199</v>
+      </c>
+      <c r="N42" s="3" t="s">
         <v>74</v>
       </c>
     </row>

--- a/data/LGP-Menu.xlsx
+++ b/data/LGP-Menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\QR1PEPF00005878\EXCELCNV\0c466152-c767-4433-9da1-dce5be5e872a\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0B67B2B-8994-4935-AE9F-A2660FDDBE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD4466E0-D0A6-4837-97F4-A572CEB602AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
